--- a/Experiment/Results/MemoryUsageSorted.xlsx
+++ b/Experiment/Results/MemoryUsageSorted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Howest\GD_J3_S2\Gradwork_2.0\Gradwork\Experiment\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B40A89-8DBA-4C55-BC95-7D071369BE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B5B93D-0FDB-40ED-A37D-E38AAA3D7370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-10790" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SSAO" sheetId="1" r:id="rId1"/>
@@ -2544,6 +2544,9 @@
     <sortCondition ref="E15:X15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D4:D15 D19:D30" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4444,6 +4447,9 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D4:D15 D19:D30" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6342,5 +6348,8 @@
     <sortCondition ref="E15:X15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D4:D15 D19:D30" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>